--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67708_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67708_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R599a4aaf0ec14c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R703e540df5ea4031"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67708_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67708_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R703e540df5ea4031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5de5998c81fc4659"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1568</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1845</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7195</x:v>
+        <x:v>      1.4343</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7195</x:v>
+        <x:v>      1.4343</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7684</x:v>
+        <x:v>      1.4620</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7684</x:v>
+        <x:v>      1.4620</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8696</x:v>
+        <x:v>      1.5175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8696</x:v>
+        <x:v>      1.5175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8184</x:v>
+        <x:v>      1.4898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9755</x:v>
+        <x:v>      1.5769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8696</x:v>
+        <x:v>      1.5175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9755</x:v>
+        <x:v>      1.5769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9755</x:v>
+        <x:v>      1.5769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0303</x:v>
+        <x:v>      1.6544</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8696</x:v>
+        <x:v>      1.5175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.0863</x:v>
+        <x:v>      1.7332</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2022</x:v>
+        <x:v>      1.8949</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4498</x:v>
+        <x:v>      2.2342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3233</x:v>
+        <x:v>      2.0619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5819</x:v>
+        <x:v>      2.4119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5819</x:v>
+        <x:v>      2.4119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7198</x:v>
+        <x:v>      2.5948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7198</x:v>
+        <x:v>      2.5948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6501</x:v>
+        <x:v>      2.5027</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7198</x:v>
+        <x:v>      2.5948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7198</x:v>
+        <x:v>      2.5948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8637</x:v>
+        <x:v>      2.7830</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8637</x:v>
+        <x:v>      2.7830</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7198</x:v>
+        <x:v>      2.5948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3233</x:v>
+        <x:v>      2.0619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4914</x:v>
+        <x:v>      1.2955</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5349</x:v>
+        <x:v>      1.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4074</x:v>
+        <x:v>      1.2400</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3669</x:v>
+        <x:v>      1.2123</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4074</x:v>
+        <x:v>      1.2400</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4074</x:v>
+        <x:v>      1.2400</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5349</x:v>
+        <x:v>      1.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5349</x:v>
+        <x:v>      1.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5794</x:v>
+        <x:v>      1.3510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4914</x:v>
+        <x:v>      1.2955</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6250</x:v>
+        <x:v>      1.3788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6250</x:v>
+        <x:v>      1.3788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5794</x:v>
+        <x:v>      1.3510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7684</x:v>
+        <x:v>      1.4620</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7684</x:v>
+        <x:v>      1.4620</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6717</x:v>
+        <x:v>      1.4065</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5349</x:v>
+        <x:v>      1.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5349</x:v>
+        <x:v>      1.3233</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6250</x:v>
+        <x:v>      1.3788</x:v>
       </x:c>
     </x:row>
     <x:row>
